--- a/artfynd/A 14508-2024 artfynd.xlsx
+++ b/artfynd/A 14508-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>116450911</v>
       </c>
       <c r="B2" t="n">
-        <v>57283</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,7 +711,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kojte (Kojte), Upl</t>
+          <t>Kojte, Kojte, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 14508-2024 artfynd.xlsx
+++ b/artfynd/A 14508-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116450911</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>57750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14508-2024 artfynd.xlsx
+++ b/artfynd/A 14508-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116450911</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14508-2024 artfynd.xlsx
+++ b/artfynd/A 14508-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116450911</v>
       </c>
       <c r="B2" t="n">
-        <v>57839</v>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14508-2024 artfynd.xlsx
+++ b/artfynd/A 14508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>116450911</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,6 +784,244 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94692596</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58212</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lappdal, Angarnssjöängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>678669</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6606614</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vada</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunnar Hesse</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunnar Hesse, Marie-Louise Hesse</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126207982</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43464</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lappdal, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>678668</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6606605</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vada</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
